--- a/informes_data/Tercera FEB/2025-26/Regular_Season/aggregate_individual/AGG_IND_DEHESAS REUNIDAS CLIMANAVAS AGROMETAL PEÑARROYA.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/aggregate_individual/AGG_IND_DEHESAS REUNIDAS CLIMANAVAS AGROMETAL PEÑARROYA.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>C. ARANDA SUAREZ</t>
+          <t>X. NEWSON</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,73 +565,73 @@
         <v>26</v>
       </c>
       <c r="D2" t="n">
-        <v>41.9773</v>
+        <v>50.475</v>
       </c>
       <c r="E2" t="n">
-        <v>41.8266</v>
+        <v>71.7448</v>
       </c>
       <c r="F2" t="n">
-        <v>0.1508000000000012</v>
+        <v>-21.2697</v>
       </c>
       <c r="G2" t="n">
-        <v>17.2811</v>
+        <v>17.9805</v>
       </c>
       <c r="H2" t="n">
-        <v>19.4786</v>
+        <v>9.279499999999999</v>
       </c>
       <c r="I2" t="n">
-        <v>-2.197499999999999</v>
+        <v>8.701200000000002</v>
       </c>
       <c r="J2" t="n">
-        <v>40.7515</v>
+        <v>62.6794</v>
       </c>
       <c r="K2" t="n">
-        <v>32.7468</v>
+        <v>37.556</v>
       </c>
       <c r="L2" t="n">
-        <v>8.004900000000001</v>
+        <v>25.1232</v>
       </c>
       <c r="M2" t="n">
-        <v>-23.4707</v>
+        <v>-44.6986</v>
       </c>
       <c r="N2" t="n">
-        <v>-13.2677</v>
+        <v>-28.2768</v>
       </c>
       <c r="O2" t="n">
-        <v>-10.2032</v>
+        <v>-16.4218</v>
       </c>
       <c r="P2" t="n">
-        <v>-14.0819</v>
+        <v>1.296600000000001</v>
       </c>
       <c r="Q2" t="n">
-        <v>-45.5804</v>
+        <v>-45.7659</v>
       </c>
       <c r="R2" t="n">
-        <v>31.4986</v>
+        <v>47.0627</v>
       </c>
       <c r="S2" t="n">
-        <v>51.057</v>
+        <v>-4.678299999999999</v>
       </c>
       <c r="T2" t="n">
-        <v>39.4296</v>
+        <v>-0.2343999999999998</v>
       </c>
       <c r="U2" t="n">
-        <v>11.6278</v>
+        <v>-4.444</v>
       </c>
       <c r="V2" t="n">
-        <v>-12.279</v>
+        <v>35.8758</v>
       </c>
       <c r="W2" t="n">
-        <v>7.2258</v>
+        <v>55.0659</v>
       </c>
       <c r="X2" t="n">
-        <v>-19.505</v>
+        <v>-19.19</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>X. NEWSON</t>
+          <t>R. SANAHUJA TRESERRAS</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,67 +643,67 @@
         <v>26</v>
       </c>
       <c r="D3" t="n">
-        <v>40.59370000000001</v>
+        <v>17.3502</v>
       </c>
       <c r="E3" t="n">
-        <v>67.4361</v>
+        <v>30.0344</v>
       </c>
       <c r="F3" t="n">
-        <v>-26.8424</v>
+        <v>-12.684</v>
       </c>
       <c r="G3" t="n">
-        <v>17.9805</v>
+        <v>29.4567</v>
       </c>
       <c r="H3" t="n">
-        <v>9.279499999999999</v>
+        <v>-13.916</v>
       </c>
       <c r="I3" t="n">
-        <v>8.701200000000002</v>
+        <v>43.3724</v>
       </c>
       <c r="J3" t="n">
-        <v>62.6794</v>
+        <v>54.687</v>
       </c>
       <c r="K3" t="n">
-        <v>37.556</v>
+        <v>4.9284</v>
       </c>
       <c r="L3" t="n">
-        <v>25.1232</v>
+        <v>49.7585</v>
       </c>
       <c r="M3" t="n">
-        <v>-44.6986</v>
+        <v>-25.2301</v>
       </c>
       <c r="N3" t="n">
-        <v>-28.2768</v>
+        <v>-18.8443</v>
       </c>
       <c r="O3" t="n">
-        <v>-16.4218</v>
+        <v>-6.3858</v>
       </c>
       <c r="P3" t="n">
-        <v>1.296600000000001</v>
+        <v>1.6676</v>
       </c>
       <c r="Q3" t="n">
-        <v>-45.7659</v>
+        <v>-33.7222</v>
       </c>
       <c r="R3" t="n">
-        <v>47.0627</v>
+        <v>35.3898</v>
       </c>
       <c r="S3" t="n">
-        <v>-14.5598</v>
+        <v>-5.4672</v>
       </c>
       <c r="T3" t="n">
-        <v>-4.5433</v>
+        <v>0.8895999999999998</v>
       </c>
       <c r="U3" t="n">
-        <v>-10.0165</v>
+        <v>-6.356</v>
       </c>
       <c r="V3" t="n">
-        <v>35.8758</v>
+        <v>-8.307399999999999</v>
       </c>
       <c r="W3" t="n">
-        <v>55.0659</v>
+        <v>8.180199999999999</v>
       </c>
       <c r="X3" t="n">
-        <v>-19.19</v>
+        <v>-16.4877</v>
       </c>
     </row>
     <row r="4">
@@ -721,13 +721,13 @@
         <v>9</v>
       </c>
       <c r="D4" t="n">
-        <v>21.9989</v>
+        <v>13.7072</v>
       </c>
       <c r="E4" t="n">
-        <v>18.6129</v>
+        <v>11.5622</v>
       </c>
       <c r="F4" t="n">
-        <v>3.3857</v>
+        <v>2.1449</v>
       </c>
       <c r="G4" t="n">
         <v>10.9177</v>
@@ -766,13 +766,13 @@
         <v>10.7466</v>
       </c>
       <c r="S4" t="n">
-        <v>10.933</v>
+        <v>2.6412</v>
       </c>
       <c r="T4" t="n">
-        <v>8.7036</v>
+        <v>1.6528</v>
       </c>
       <c r="U4" t="n">
-        <v>2.2292</v>
+        <v>0.9884000000000001</v>
       </c>
       <c r="V4" t="n">
         <v>-1.8898</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>R. SANAHUJA TRESERRAS</t>
+          <t>C. ARANDA SUAREZ</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>26</v>
       </c>
       <c r="D5" t="n">
-        <v>4.2541</v>
+        <v>10.5547</v>
       </c>
       <c r="E5" t="n">
-        <v>22.1021</v>
+        <v>18.7155</v>
       </c>
       <c r="F5" t="n">
-        <v>-17.8483</v>
+        <v>-8.160599999999999</v>
       </c>
       <c r="G5" t="n">
-        <v>29.4567</v>
+        <v>17.2811</v>
       </c>
       <c r="H5" t="n">
-        <v>-13.916</v>
+        <v>19.4786</v>
       </c>
       <c r="I5" t="n">
-        <v>43.3724</v>
+        <v>-2.197499999999999</v>
       </c>
       <c r="J5" t="n">
-        <v>54.687</v>
+        <v>40.7515</v>
       </c>
       <c r="K5" t="n">
-        <v>4.9284</v>
+        <v>32.7468</v>
       </c>
       <c r="L5" t="n">
-        <v>49.7585</v>
+        <v>8.004900000000001</v>
       </c>
       <c r="M5" t="n">
-        <v>-25.2301</v>
+        <v>-23.4707</v>
       </c>
       <c r="N5" t="n">
-        <v>-18.8443</v>
+        <v>-13.2677</v>
       </c>
       <c r="O5" t="n">
-        <v>-6.3858</v>
+        <v>-10.2032</v>
       </c>
       <c r="P5" t="n">
-        <v>1.6676</v>
+        <v>-14.0819</v>
       </c>
       <c r="Q5" t="n">
-        <v>-33.7222</v>
+        <v>-45.5804</v>
       </c>
       <c r="R5" t="n">
-        <v>35.3898</v>
+        <v>31.4986</v>
       </c>
       <c r="S5" t="n">
-        <v>-18.563</v>
+        <v>19.6342</v>
       </c>
       <c r="T5" t="n">
-        <v>-7.0431</v>
+        <v>16.3182</v>
       </c>
       <c r="U5" t="n">
-        <v>-11.5201</v>
+        <v>3.3161</v>
       </c>
       <c r="V5" t="n">
-        <v>-8.307399999999999</v>
+        <v>-12.279</v>
       </c>
       <c r="W5" t="n">
-        <v>8.180199999999999</v>
+        <v>7.2258</v>
       </c>
       <c r="X5" t="n">
-        <v>-16.4877</v>
+        <v>-19.505</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A. ELIAS GALLEGOS</t>
+          <t>J. VARO BARBANCHO</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -874,76 +874,76 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="D6" t="n">
-        <v>3.2434</v>
+        <v>6.5623</v>
       </c>
       <c r="E6" t="n">
-        <v>10.4939</v>
+        <v>25.021</v>
       </c>
       <c r="F6" t="n">
-        <v>-7.2502</v>
+        <v>-18.459</v>
       </c>
       <c r="G6" t="n">
-        <v>7.492699999999999</v>
+        <v>23.6593</v>
       </c>
       <c r="H6" t="n">
-        <v>3.8146</v>
+        <v>-2.2233</v>
       </c>
       <c r="I6" t="n">
-        <v>3.6781</v>
+        <v>25.8828</v>
       </c>
       <c r="J6" t="n">
-        <v>18.0052</v>
+        <v>55.4718</v>
       </c>
       <c r="K6" t="n">
-        <v>12.1329</v>
+        <v>16.7517</v>
       </c>
       <c r="L6" t="n">
-        <v>5.872599999999999</v>
+        <v>38.7202</v>
       </c>
       <c r="M6" t="n">
-        <v>-10.5127</v>
+        <v>-31.8124</v>
       </c>
       <c r="N6" t="n">
-        <v>-8.318200000000001</v>
+        <v>-18.9748</v>
       </c>
       <c r="O6" t="n">
-        <v>-2.1947</v>
+        <v>-12.8373</v>
       </c>
       <c r="P6" t="n">
-        <v>1.853</v>
+        <v>-3.1498</v>
       </c>
       <c r="Q6" t="n">
-        <v>-14.4524</v>
+        <v>-33.7223</v>
       </c>
       <c r="R6" t="n">
-        <v>16.3053</v>
+        <v>30.5722</v>
       </c>
       <c r="S6" t="n">
-        <v>5.1001</v>
+        <v>-4.5729</v>
       </c>
       <c r="T6" t="n">
-        <v>4.426</v>
+        <v>-2.39</v>
       </c>
       <c r="U6" t="n">
-        <v>0.6740999999999999</v>
+        <v>-2.1828</v>
       </c>
       <c r="V6" t="n">
-        <v>-11.2023</v>
+        <v>-9.374499999999999</v>
       </c>
       <c r="W6" t="n">
-        <v>2.5149</v>
+        <v>5.6616</v>
       </c>
       <c r="X6" t="n">
-        <v>-13.7173</v>
+        <v>-15.036</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>K. SECK DIOP</t>
+          <t>A. ELIAS GALLEGOS</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -952,76 +952,76 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>6</v>
+        <v>22</v>
       </c>
       <c r="D7" t="n">
-        <v>1.7571</v>
+        <v>0.3088999999999995</v>
       </c>
       <c r="E7" t="n">
-        <v>2.576499999999999</v>
+        <v>7.849699999999999</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.8192999999999999</v>
+        <v>-7.540600000000001</v>
       </c>
       <c r="G7" t="n">
-        <v>1.8401</v>
+        <v>7.492699999999999</v>
       </c>
       <c r="H7" t="n">
-        <v>1.1931</v>
+        <v>3.8146</v>
       </c>
       <c r="I7" t="n">
-        <v>0.6472</v>
+        <v>3.6781</v>
       </c>
       <c r="J7" t="n">
-        <v>5.7088</v>
+        <v>18.0052</v>
       </c>
       <c r="K7" t="n">
-        <v>3.0121</v>
+        <v>12.1329</v>
       </c>
       <c r="L7" t="n">
-        <v>2.697</v>
+        <v>5.872599999999999</v>
       </c>
       <c r="M7" t="n">
-        <v>-3.8688</v>
+        <v>-10.5127</v>
       </c>
       <c r="N7" t="n">
-        <v>-1.8191</v>
+        <v>-8.318200000000001</v>
       </c>
       <c r="O7" t="n">
-        <v>-2.0499</v>
+        <v>-2.1947</v>
       </c>
       <c r="P7" t="n">
-        <v>-0.9263999999999999</v>
+        <v>1.853</v>
       </c>
       <c r="Q7" t="n">
-        <v>-8.523199999999999</v>
+        <v>-14.4524</v>
       </c>
       <c r="R7" t="n">
-        <v>7.5968</v>
+        <v>16.3053</v>
       </c>
       <c r="S7" t="n">
-        <v>2.1653</v>
+        <v>2.1659</v>
       </c>
       <c r="T7" t="n">
-        <v>2.8753</v>
+        <v>1.7818</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.7099</v>
+        <v>0.3839</v>
       </c>
       <c r="V7" t="n">
-        <v>-1.3217</v>
+        <v>-11.2023</v>
       </c>
       <c r="W7" t="n">
-        <v>2.5155</v>
+        <v>2.5149</v>
       </c>
       <c r="X7" t="n">
-        <v>-3.8371</v>
+        <v>-13.7173</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>J. VARO BARBANCHO</t>
+          <t>K. SECK DIOP</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1030,70 +1030,70 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>19</v>
+        <v>6</v>
       </c>
       <c r="D8" t="n">
-        <v>-2.154399999999999</v>
+        <v>0.2345000000000003</v>
       </c>
       <c r="E8" t="n">
-        <v>16.3053</v>
+        <v>1.890899999999999</v>
       </c>
       <c r="F8" t="n">
-        <v>-18.4596</v>
+        <v>-1.6563</v>
       </c>
       <c r="G8" t="n">
-        <v>23.6593</v>
+        <v>1.8401</v>
       </c>
       <c r="H8" t="n">
-        <v>-2.2233</v>
+        <v>1.1931</v>
       </c>
       <c r="I8" t="n">
-        <v>25.8828</v>
+        <v>0.6472</v>
       </c>
       <c r="J8" t="n">
-        <v>55.4718</v>
+        <v>5.7088</v>
       </c>
       <c r="K8" t="n">
-        <v>16.7517</v>
+        <v>3.0121</v>
       </c>
       <c r="L8" t="n">
-        <v>38.7202</v>
+        <v>2.697</v>
       </c>
       <c r="M8" t="n">
-        <v>-31.8124</v>
+        <v>-3.8688</v>
       </c>
       <c r="N8" t="n">
-        <v>-18.9748</v>
+        <v>-1.8191</v>
       </c>
       <c r="O8" t="n">
-        <v>-12.8373</v>
+        <v>-2.0499</v>
       </c>
       <c r="P8" t="n">
-        <v>-3.1498</v>
+        <v>-0.9263999999999999</v>
       </c>
       <c r="Q8" t="n">
-        <v>-33.7223</v>
+        <v>-8.523199999999999</v>
       </c>
       <c r="R8" t="n">
-        <v>30.5722</v>
+        <v>7.5968</v>
       </c>
       <c r="S8" t="n">
-        <v>-13.2894</v>
+        <v>0.6425999999999999</v>
       </c>
       <c r="T8" t="n">
-        <v>-11.1056</v>
+        <v>2.1897</v>
       </c>
       <c r="U8" t="n">
-        <v>-2.1837</v>
+        <v>-1.547</v>
       </c>
       <c r="V8" t="n">
-        <v>-9.374499999999999</v>
+        <v>-1.3217</v>
       </c>
       <c r="W8" t="n">
-        <v>5.6616</v>
+        <v>2.5155</v>
       </c>
       <c r="X8" t="n">
-        <v>-15.036</v>
+        <v>-3.8371</v>
       </c>
     </row>
     <row r="9">
@@ -1111,13 +1111,13 @@
         <v>6</v>
       </c>
       <c r="D9" t="n">
-        <v>-3.1633</v>
+        <v>-2.3782</v>
       </c>
       <c r="E9" t="n">
-        <v>-2.8762</v>
+        <v>-2.3866</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.2872</v>
+        <v>0.008299999999999835</v>
       </c>
       <c r="G9" t="n">
         <v>-1.6964</v>
@@ -1156,13 +1156,13 @@
         <v>0.9265</v>
       </c>
       <c r="S9" t="n">
-        <v>-1.0788</v>
+        <v>-0.2937</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.4923</v>
+        <v>-0.002799999999999997</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.5865</v>
+        <v>-0.291</v>
       </c>
       <c r="V9" t="n">
         <v>-0.9438</v>
@@ -1177,7 +1177,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>M. MARTIN MONTERRUBIO</t>
+          <t>P. VILLAREJO CALATAYUD</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1186,76 +1186,76 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>1</v>
+        <v>26</v>
       </c>
       <c r="D10" t="n">
-        <v>-7.7577</v>
+        <v>-7.219100000000001</v>
       </c>
       <c r="E10" t="n">
-        <v>-3.078</v>
+        <v>8.877599999999999</v>
       </c>
       <c r="F10" t="n">
-        <v>-4.6797</v>
+        <v>-16.0965</v>
       </c>
       <c r="G10" t="n">
-        <v>-1.8135</v>
+        <v>4.983299999999999</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.8658</v>
+        <v>0.9790000000000002</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.9477</v>
+        <v>4.004099999999999</v>
       </c>
       <c r="J10" t="n">
-        <v>0.2256</v>
+        <v>47.3114</v>
       </c>
       <c r="K10" t="n">
-        <v>0.7126</v>
+        <v>29.6565</v>
       </c>
       <c r="L10" t="n">
-        <v>-0.487</v>
+        <v>17.6547</v>
       </c>
       <c r="M10" t="n">
-        <v>-2.0391</v>
+        <v>-42.3279</v>
       </c>
       <c r="N10" t="n">
-        <v>-1.5784</v>
+        <v>-28.6776</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.4607</v>
+        <v>-13.6505</v>
       </c>
       <c r="P10" t="n">
-        <v>-2.4087</v>
+        <v>-19.2701</v>
       </c>
       <c r="Q10" t="n">
-        <v>-2.7793</v>
+        <v>-60.7742</v>
       </c>
       <c r="R10" t="n">
-        <v>0.3706</v>
+        <v>41.5043</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.3877</v>
+        <v>-2.188</v>
       </c>
       <c r="T10" t="n">
-        <v>0.1057</v>
+        <v>-2.2024</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.4934</v>
+        <v>0.01430000000000009</v>
       </c>
       <c r="V10" t="n">
-        <v>-3.1477</v>
+        <v>9.255599999999999</v>
       </c>
       <c r="W10" t="n">
-        <v>-0.63</v>
+        <v>24.543</v>
       </c>
       <c r="X10" t="n">
-        <v>-2.5177</v>
+        <v>-15.2874</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>R. URBANO MORENO</t>
+          <t>M. MARTIN MONTERRUBIO</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1264,76 +1264,76 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-8.412800000000001</v>
+        <v>-7.733</v>
       </c>
       <c r="E11" t="n">
-        <v>-4.0373</v>
+        <v>-3.078</v>
       </c>
       <c r="F11" t="n">
-        <v>-4.3756</v>
+        <v>-4.6551</v>
       </c>
       <c r="G11" t="n">
-        <v>-1.6415</v>
+        <v>-1.8135</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.9162000000000001</v>
+        <v>-0.8658</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.7252</v>
+        <v>-0.9477</v>
       </c>
       <c r="J11" t="n">
-        <v>1.1392</v>
+        <v>0.2256</v>
       </c>
       <c r="K11" t="n">
-        <v>2.2953</v>
+        <v>0.7126</v>
       </c>
       <c r="L11" t="n">
-        <v>-1.156300000000001</v>
+        <v>-0.487</v>
       </c>
       <c r="M11" t="n">
-        <v>-2.7806</v>
+        <v>-2.0391</v>
       </c>
       <c r="N11" t="n">
-        <v>-3.2117</v>
+        <v>-1.5784</v>
       </c>
       <c r="O11" t="n">
-        <v>0.4310000000000002</v>
+        <v>-0.4607</v>
       </c>
       <c r="P11" t="n">
-        <v>-4.6322</v>
+        <v>-2.4087</v>
       </c>
       <c r="Q11" t="n">
-        <v>-14.4524</v>
+        <v>-2.7793</v>
       </c>
       <c r="R11" t="n">
-        <v>9.8202</v>
+        <v>0.3706</v>
       </c>
       <c r="S11" t="n">
-        <v>3.21</v>
+        <v>-0.3631</v>
       </c>
       <c r="T11" t="n">
-        <v>2.0382</v>
+        <v>0.1057</v>
       </c>
       <c r="U11" t="n">
-        <v>1.1718</v>
+        <v>-0.4688</v>
       </c>
       <c r="V11" t="n">
-        <v>-5.3493</v>
+        <v>-3.1477</v>
       </c>
       <c r="W11" t="n">
-        <v>7.2376</v>
+        <v>-0.63</v>
       </c>
       <c r="X11" t="n">
-        <v>-12.5869</v>
+        <v>-2.5177</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>P. VILLAREJO CALATAYUD</t>
+          <t>R. URBANO MORENO</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1342,70 +1342,70 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>26</v>
+        <v>9</v>
       </c>
       <c r="D12" t="n">
-        <v>-17.7967</v>
+        <v>-8.682500000000001</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.3279000000000006</v>
+        <v>-4.6249</v>
       </c>
       <c r="F12" t="n">
-        <v>-17.4687</v>
+        <v>-4.0578</v>
       </c>
       <c r="G12" t="n">
-        <v>4.983299999999999</v>
+        <v>-1.6415</v>
       </c>
       <c r="H12" t="n">
-        <v>0.9790000000000002</v>
+        <v>-0.9162000000000001</v>
       </c>
       <c r="I12" t="n">
-        <v>4.004099999999999</v>
+        <v>-0.7252</v>
       </c>
       <c r="J12" t="n">
-        <v>47.3114</v>
+        <v>1.1392</v>
       </c>
       <c r="K12" t="n">
-        <v>29.6565</v>
+        <v>2.2953</v>
       </c>
       <c r="L12" t="n">
-        <v>17.6547</v>
+        <v>-1.156300000000001</v>
       </c>
       <c r="M12" t="n">
-        <v>-42.3279</v>
+        <v>-2.7806</v>
       </c>
       <c r="N12" t="n">
-        <v>-28.6776</v>
+        <v>-3.2117</v>
       </c>
       <c r="O12" t="n">
-        <v>-13.6505</v>
+        <v>0.4310000000000002</v>
       </c>
       <c r="P12" t="n">
-        <v>-19.2701</v>
+        <v>-4.6322</v>
       </c>
       <c r="Q12" t="n">
-        <v>-60.7742</v>
+        <v>-14.4524</v>
       </c>
       <c r="R12" t="n">
-        <v>41.5043</v>
+        <v>9.8202</v>
       </c>
       <c r="S12" t="n">
-        <v>-12.7657</v>
+        <v>2.9403</v>
       </c>
       <c r="T12" t="n">
-        <v>-11.4076</v>
+        <v>1.4507</v>
       </c>
       <c r="U12" t="n">
-        <v>-1.3579</v>
+        <v>1.4895</v>
       </c>
       <c r="V12" t="n">
-        <v>9.255599999999999</v>
+        <v>-5.3493</v>
       </c>
       <c r="W12" t="n">
-        <v>24.543</v>
+        <v>7.2376</v>
       </c>
       <c r="X12" t="n">
-        <v>-15.2874</v>
+        <v>-12.5869</v>
       </c>
     </row>
     <row r="13">
@@ -1423,13 +1423,13 @@
         <v>24</v>
       </c>
       <c r="D13" t="n">
-        <v>-18.1442</v>
+        <v>-13.6215</v>
       </c>
       <c r="E13" t="n">
-        <v>6.0123</v>
+        <v>6.5999</v>
       </c>
       <c r="F13" t="n">
-        <v>-24.1564</v>
+        <v>-20.2215</v>
       </c>
       <c r="G13" t="n">
         <v>8.8005</v>
@@ -1468,13 +1468,13 @@
         <v>33.1664</v>
       </c>
       <c r="S13" t="n">
-        <v>-6.645900000000001</v>
+        <v>-2.1232</v>
       </c>
       <c r="T13" t="n">
-        <v>2.7536</v>
+        <v>3.341299999999999</v>
       </c>
       <c r="U13" t="n">
-        <v>-9.3995</v>
+        <v>-5.4643</v>
       </c>
       <c r="V13" t="n">
         <v>-1.9556</v>
@@ -1489,7 +1489,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>R. MERINO LUQUE</t>
+          <t>U. FRISCIA PEREZ</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1498,76 +1498,76 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="D14" t="n">
-        <v>-18.242</v>
+        <v>-16.571</v>
       </c>
       <c r="E14" t="n">
-        <v>1.3579</v>
+        <v>-14.9326</v>
       </c>
       <c r="F14" t="n">
-        <v>-19.5996</v>
+        <v>-1.6383</v>
       </c>
       <c r="G14" t="n">
-        <v>-9.807499999999999</v>
+        <v>-6.9075</v>
       </c>
       <c r="H14" t="n">
-        <v>-6.8256</v>
+        <v>-5.1145</v>
       </c>
       <c r="I14" t="n">
-        <v>-2.9817</v>
+        <v>-1.7932</v>
       </c>
       <c r="J14" t="n">
-        <v>12.2646</v>
+        <v>-1.334900000000001</v>
       </c>
       <c r="K14" t="n">
-        <v>9.3354</v>
+        <v>-1.8446</v>
       </c>
       <c r="L14" t="n">
-        <v>2.9294</v>
+        <v>0.5096000000000001</v>
       </c>
       <c r="M14" t="n">
-        <v>-22.0722</v>
+        <v>-5.5724</v>
       </c>
       <c r="N14" t="n">
-        <v>-16.1611</v>
+        <v>-3.2698</v>
       </c>
       <c r="O14" t="n">
-        <v>-5.911200000000001</v>
+        <v>-2.3028</v>
       </c>
       <c r="P14" t="n">
-        <v>0</v>
+        <v>-3.8911</v>
       </c>
       <c r="Q14" t="n">
-        <v>-21.1229</v>
+        <v>-14.4523</v>
       </c>
       <c r="R14" t="n">
-        <v>21.1226</v>
+        <v>10.5613</v>
       </c>
       <c r="S14" t="n">
-        <v>-1.7076</v>
+        <v>-3.3822</v>
       </c>
       <c r="T14" t="n">
-        <v>-1.4261</v>
+        <v>-1.0328</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.2817</v>
+        <v>-2.3493</v>
       </c>
       <c r="V14" t="n">
-        <v>-6.7268</v>
+        <v>-2.3904</v>
       </c>
       <c r="W14" t="n">
-        <v>11.6421</v>
+        <v>1.8877</v>
       </c>
       <c r="X14" t="n">
-        <v>-18.3688</v>
+        <v>-4.2782</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>U. FRISCIA PEREZ</t>
+          <t>R. MERINO LUQUE</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1576,70 +1576,70 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="D15" t="n">
-        <v>-20.5691</v>
+        <v>-20.5498</v>
       </c>
       <c r="E15" t="n">
-        <v>-17.1848</v>
+        <v>-0.6007000000000001</v>
       </c>
       <c r="F15" t="n">
-        <v>-3.3842</v>
+        <v>-19.9489</v>
       </c>
       <c r="G15" t="n">
-        <v>-6.9075</v>
+        <v>-9.807499999999999</v>
       </c>
       <c r="H15" t="n">
-        <v>-5.1145</v>
+        <v>-6.8256</v>
       </c>
       <c r="I15" t="n">
-        <v>-1.7932</v>
+        <v>-2.9817</v>
       </c>
       <c r="J15" t="n">
-        <v>-1.334900000000001</v>
+        <v>12.2646</v>
       </c>
       <c r="K15" t="n">
-        <v>-1.8446</v>
+        <v>9.3354</v>
       </c>
       <c r="L15" t="n">
-        <v>0.5096000000000001</v>
+        <v>2.9294</v>
       </c>
       <c r="M15" t="n">
-        <v>-5.5724</v>
+        <v>-22.0722</v>
       </c>
       <c r="N15" t="n">
-        <v>-3.2698</v>
+        <v>-16.1611</v>
       </c>
       <c r="O15" t="n">
-        <v>-2.3028</v>
+        <v>-5.911200000000001</v>
       </c>
       <c r="P15" t="n">
-        <v>-3.8911</v>
+        <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>-14.4523</v>
+        <v>-21.1229</v>
       </c>
       <c r="R15" t="n">
-        <v>10.5613</v>
+        <v>21.1226</v>
       </c>
       <c r="S15" t="n">
-        <v>-7.3804</v>
+        <v>-4.0153</v>
       </c>
       <c r="T15" t="n">
-        <v>-3.2853</v>
+        <v>-3.3846</v>
       </c>
       <c r="U15" t="n">
-        <v>-4.095</v>
+        <v>-0.6309000000000001</v>
       </c>
       <c r="V15" t="n">
-        <v>-2.3904</v>
+        <v>-6.7268</v>
       </c>
       <c r="W15" t="n">
-        <v>1.8877</v>
+        <v>11.6421</v>
       </c>
       <c r="X15" t="n">
-        <v>-4.2782</v>
+        <v>-18.3688</v>
       </c>
     </row>
     <row r="16">
@@ -1657,13 +1657,13 @@
         <v>22</v>
       </c>
       <c r="D16" t="n">
-        <v>-26.2306</v>
+        <v>-21.2911</v>
       </c>
       <c r="E16" t="n">
-        <v>-7.8655</v>
+        <v>-5.319199999999999</v>
       </c>
       <c r="F16" t="n">
-        <v>-18.3652</v>
+        <v>-15.9718</v>
       </c>
       <c r="G16" t="n">
         <v>-2.5608</v>
@@ -1702,13 +1702,13 @@
         <v>17.4168</v>
       </c>
       <c r="S16" t="n">
-        <v>-7.3169</v>
+        <v>-2.3772</v>
       </c>
       <c r="T16" t="n">
-        <v>-3.7827</v>
+        <v>-1.2363</v>
       </c>
       <c r="U16" t="n">
-        <v>-3.5337</v>
+        <v>-1.1405</v>
       </c>
       <c r="V16" t="n">
         <v>-12.6477</v>
@@ -1735,13 +1735,13 @@
         <v>26</v>
       </c>
       <c r="D17" t="n">
-        <v>-8.646300000000007</v>
+        <v>1.146599999999996</v>
       </c>
       <c r="E17" t="n">
-        <v>151.3539</v>
+        <v>151.354</v>
       </c>
       <c r="F17" t="n">
-        <v>-159.9999</v>
+        <v>-150.2069</v>
       </c>
       <c r="G17" t="n">
         <v>97.98469999999999</v>
@@ -1768,7 +1768,7 @@
         <v>-178.0135</v>
       </c>
       <c r="O17" t="n">
-        <v>-91.08770000000001</v>
+        <v>-91.0877</v>
       </c>
       <c r="P17" t="n">
         <v>-62.9983</v>
@@ -1780,13 +1780,13 @@
         <v>314.0607</v>
       </c>
       <c r="S17" t="n">
-        <v>-11.22979999999999</v>
+        <v>-1.436899999999999</v>
       </c>
       <c r="T17" t="n">
-        <v>17.246</v>
+        <v>17.2465</v>
       </c>
       <c r="U17" t="n">
-        <v>-28.475</v>
+        <v>-18.6824</v>
       </c>
       <c r="V17" t="n">
         <v>-32.4046</v>
